--- a/artfynd/A 7443-2025 artfynd.xlsx
+++ b/artfynd/A 7443-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124159632</v>
+        <v>124159616</v>
       </c>
       <c r="B2" t="n">
         <v>79869</v>
@@ -721,7 +721,7 @@
         <v>510172</v>
       </c>
       <c r="R2" t="n">
-        <v>6953489</v>
+        <v>6953511</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124159616</v>
+        <v>124159632</v>
       </c>
       <c r="B3" t="n">
         <v>79869</v>
@@ -827,7 +827,7 @@
         <v>510172</v>
       </c>
       <c r="R3" t="n">
-        <v>6953511</v>
+        <v>6953489</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 7443-2025 artfynd.xlsx
+++ b/artfynd/A 7443-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124159616</v>
+        <v>124159632</v>
       </c>
       <c r="B2" t="n">
         <v>79891</v>
@@ -721,7 +721,7 @@
         <v>510172</v>
       </c>
       <c r="R2" t="n">
-        <v>6953511</v>
+        <v>6953489</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124159632</v>
+        <v>124159616</v>
       </c>
       <c r="B3" t="n">
         <v>79891</v>
@@ -827,7 +827,7 @@
         <v>510172</v>
       </c>
       <c r="R3" t="n">
-        <v>6953489</v>
+        <v>6953511</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 7443-2025 artfynd.xlsx
+++ b/artfynd/A 7443-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124159632</v>
+        <v>124159616</v>
       </c>
       <c r="B2" t="n">
         <v>79891</v>
@@ -721,7 +721,7 @@
         <v>510172</v>
       </c>
       <c r="R2" t="n">
-        <v>6953489</v>
+        <v>6953511</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124159616</v>
+        <v>124159632</v>
       </c>
       <c r="B3" t="n">
         <v>79891</v>
@@ -827,7 +827,7 @@
         <v>510172</v>
       </c>
       <c r="R3" t="n">
-        <v>6953511</v>
+        <v>6953489</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
